--- a/Program/CAISO-API/Data/CAISO_NG_2026.xlsx
+++ b/Program/CAISO-API/Data/CAISO_NG_2026.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filter_Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page1_GenFuel" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page4_Generator" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page5_FuelReceipts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛选说明'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Filter_Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Page1_GenFuel'!$A$1:$CS$162</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page4_Generator'!$A$1:$AB$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page5_FuelReceipts'!$A$1:$AE$134</definedName>
@@ -201,8 +201,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -235,8 +235,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -445,43 +445,43 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>数据年份</t>
+          <t>Data Year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>输出 Sheet</t>
+          <t>Output Sheet</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>源 Sheet</t>
+          <t>Source Sheet</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>筛选规则</t>
+          <t>Filter Rule</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>记录数</t>
+          <t>Record Count</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>电厂数</t>
+          <t>Plant Count</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Balancing Authority Code=CISO 且 Reported Fuel Type Code=NG</t>
+          <t>Balancing Authority Code=CISO and Reported Fuel Type Code=NG</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -527,7 +527,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Balancing Authority Code=CISO，且 (Plant Id, Prime Mover) 在 Page 1 的 CISO+NG 数据中</t>
+          <t>Balancing Authority Code=CISO and (Plant Id, Prime Mover) appears in the CISO+NG data on Page 1</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -553,7 +553,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Balancing Authority Code=CISO 且 ENERGY_SOURCE=NG</t>
+          <t>Balancing Authority Code=CISO and ENERGY_SOURCE=NG</t>
         </is>
       </c>
       <c r="E4" t="n">
